--- a/datos/PrTest 140826.xlsx
+++ b/datos/PrTest 140826.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jorge/Desktop/AUTOESCUELA/datos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEFD9D40-523B-334F-896C-AEF414A80674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72E5DFB6-A217-BA40-84BF-5C0CFD6826FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="23220" windowHeight="16820" xr2:uid="{AE6512D7-AD52-4543-8CDE-87DCF5042393}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="151">
   <si>
     <t>Pregunta</t>
   </si>
@@ -62,15 +62,6 @@
     <t>El conductor, al circular marcha atrás para estacionar, ¿debe llevar puesto el cinturón de seguridad?</t>
   </si>
   <si>
-    <t>A) Sí, debe llevarlo abrochado hasta que el vehículo esté inmovilizado.</t>
-  </si>
-  <si>
-    <t>B) No, no es obligatorio.</t>
-  </si>
-  <si>
-    <t>C) Solo podrá quitárselo si es taxista o repartidor.</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
@@ -80,15 +71,6 @@
     <t>Cuando las ruedas llevan poco aire...</t>
   </si>
   <si>
-    <t>A) se desgastan más por los lados.</t>
-  </si>
-  <si>
-    <t>B) se desgastan más por el centro.</t>
-  </si>
-  <si>
-    <t>C) se desgastan igual por los lados que por el centro.</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -98,45 +80,18 @@
     <t>En un turismo que arrastra un remolque ligero, ¿es obligatorio llevar extintor?</t>
   </si>
   <si>
-    <t>A) Sí.</t>
-  </si>
-  <si>
-    <t>B) No, es aconsejable.</t>
-  </si>
-  <si>
-    <t>C) No.</t>
-  </si>
-  <si>
     <t>imagenes/PT140803.png</t>
   </si>
   <si>
     <t>¿Es recomendable revisar el funcionamiento del cinturón de seguridad después de sufrir un accidente grave?</t>
   </si>
   <si>
-    <t>A) Sí, puede haberse deteriorado el trenzado o los sistemas de anclaje.</t>
-  </si>
-  <si>
-    <t>B) No, es un elemento de seguridad que no es necesario revisar nunca.</t>
-  </si>
-  <si>
-    <t>C) Sólo si el cinturón no ha funcionado correctamente durante el accidente.</t>
-  </si>
-  <si>
     <t>imagenes/PT140804.png</t>
   </si>
   <si>
     <t>La depresión es una enfermedad…</t>
   </si>
   <si>
-    <t>A) que provoca una alteración del estado de ánimo que no es peligrosa para conducir.</t>
-  </si>
-  <si>
-    <t>B) que siempre es leve.</t>
-  </si>
-  <si>
-    <t>C) que puede ser peligrosa para conducir con seguridad.</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
@@ -146,361 +101,397 @@
     <t>Para incorporarse a una vía por un carril de aceleración, ¿en qué punto debe cerciorarse de que puede realizar la maniobra sin peligro?</t>
   </si>
   <si>
-    <t>A) Al final del carril de aceleración.</t>
-  </si>
-  <si>
-    <t>B) Al principio del carril de aceleración.</t>
-  </si>
-  <si>
-    <t>C) Al principio o al final del carril de aceleración, es indiferente.</t>
-  </si>
-  <si>
     <t>imagenes/PT140806.png</t>
   </si>
   <si>
     <t>La señal, ¿permite circular con un ciclomotor?</t>
   </si>
   <si>
-    <t>A) Sí, porque no es un vehículo a motor.</t>
-  </si>
-  <si>
-    <t>B) No.</t>
-  </si>
-  <si>
-    <t>C) Sí, porque la vía es para peatones</t>
-  </si>
-  <si>
     <t>imagenes/PT140807.png</t>
   </si>
   <si>
     <t>Las anfetaminas, ¿son peligrosas para conducir?</t>
   </si>
   <si>
-    <t>B) No, porque son tranquilizantes.</t>
-  </si>
-  <si>
-    <t>C) No, porque retrasan la aparición de sueño.</t>
-  </si>
-  <si>
     <t>imagenes/PT140808.png</t>
   </si>
   <si>
     <t>Qué se debe hacer antes de poner combustible?</t>
   </si>
   <si>
-    <t>A) Sólo es necesario apagar el motor, las luces y la radio.</t>
-  </si>
-  <si>
-    <t>B) Sólo es necesario apagar el motor y las luces.</t>
-  </si>
-  <si>
-    <t>C) Apagar el motor, las luces, los aparatos eléctricos y los teléfonos móviles.</t>
-  </si>
-  <si>
     <t>imagenes/PT140809.png</t>
   </si>
   <si>
     <t>En las motocicletas, la postura del conductor ha de ser...</t>
   </si>
   <si>
-    <t>A) lo más aerodinámica posible, encorvando el cuerpo cuanto más mejor.</t>
-  </si>
-  <si>
-    <t>B) un poco forzada, para evitar relajamientos.</t>
-  </si>
-  <si>
-    <t>C) suelta y no forzada, sin encorvar el cuerpo más de lo necesario.</t>
-  </si>
-  <si>
     <t>imagenes/PT140810.png</t>
   </si>
   <si>
     <t>El permiso de circulación es obligatorio para los remolques y semirremolques...</t>
   </si>
   <si>
-    <t>A) que tengan una MMA. no superior a 750 kg.</t>
-  </si>
-  <si>
-    <t>B) que tengan una MMA. superior a 750 kg.</t>
-  </si>
-  <si>
-    <t>C) cualquiera que sea su MMA.</t>
-  </si>
-  <si>
     <t>imagenes/PT140811.png</t>
   </si>
   <si>
     <t>Los agentes de tráfico ¿pueden hacer señales ópticas y acústicas?</t>
   </si>
   <si>
-    <t>A) No, sólo pueden hacer señales ópticas</t>
-  </si>
-  <si>
-    <t>B) No, sólo pueden hacer señales acústicas</t>
-  </si>
-  <si>
-    <t>C) Sí, pueden hacer señales ópticas y acústicas</t>
-  </si>
-  <si>
     <t>imagenes/PT140812.png</t>
   </si>
   <si>
     <t>¿Qué indica la señal?</t>
   </si>
   <si>
-    <t>A) Una intersección con cuatro o más vías.</t>
-  </si>
-  <si>
-    <t>B) Una incorporación por la derecha.</t>
-  </si>
-  <si>
-    <t>C) Un paso a nivel con barreras.</t>
-  </si>
-  <si>
     <t>imagenes/PT140813.png</t>
   </si>
   <si>
     <t>¿Cuáles son habitualmente las ruedas directrices de un automóvil?</t>
   </si>
   <si>
-    <t>A) Las delanteras.</t>
-  </si>
-  <si>
-    <t>B) Las traseras.</t>
-  </si>
-  <si>
-    <t>C) Ningunas, la dirección está en la caja de cambios.</t>
-  </si>
-  <si>
     <t>imagenes/PT140814.png</t>
   </si>
   <si>
     <t>¿Puede el titular de una licencia A conducir motocicletas con sidecar?</t>
   </si>
   <si>
-    <t>A) No.</t>
-  </si>
-  <si>
-    <t>B) Sí.</t>
-  </si>
-  <si>
-    <t>C) Sí, si la motocicleta supera los 125 cm3.</t>
-  </si>
-  <si>
     <t>imagenes/PT140815.png</t>
   </si>
   <si>
     <t>¿Quién deberá abonar los gastos que ocasione la inmovilización de un vehículo por parte de la autoridad?</t>
   </si>
   <si>
-    <t>A) El titular del vehículo.</t>
-  </si>
-  <si>
-    <t>B) Nadie, por qué la inmovilización no tiene gastos.</t>
-  </si>
-  <si>
-    <t>C) Los agentes de circulación.</t>
-  </si>
-  <si>
     <t>imagenes/PT140816.png</t>
   </si>
   <si>
     <t>¿De cuál de los siguientes factores NO depende el consumo de carburante?</t>
   </si>
   <si>
-    <t>A) La señalización</t>
-  </si>
-  <si>
-    <t>B) Las condiciones de la vía</t>
-  </si>
-  <si>
-    <t>C) El tipo de carburante</t>
-  </si>
-  <si>
     <t>imagenes/PT140817.png</t>
   </si>
   <si>
     <t>Si un agente de la autoridad balancea una luz roja dirigiéndose a su vehículo en un tramo dónde se realizan obras, ¿a qué obliga?</t>
   </si>
   <si>
-    <t>A) A realizar un cambio de sentido.</t>
-  </si>
-  <si>
-    <t>B) A detenerse.</t>
-  </si>
-  <si>
-    <t>C) A extremar la precaución.</t>
-  </si>
-  <si>
     <t>imagenes/PT140818.png</t>
   </si>
   <si>
     <t>Se pueden abrir las puertas antes de la completa inmovilización del vehículo?</t>
   </si>
   <si>
-    <t>A) Únicamente estará permitido en caso de urgencia</t>
-  </si>
-  <si>
-    <t>B) Sí, está permitido y recomendado</t>
-  </si>
-  <si>
-    <t>C) No, está prohibido</t>
-  </si>
-  <si>
     <t>imagenes/PT140819.png</t>
   </si>
   <si>
     <t>Esta señal indica que se aproxima a un cruce...</t>
   </si>
   <si>
-    <t>A) Sin preferencia de paso.</t>
-  </si>
-  <si>
-    <t>B) Con preferencia de paso.</t>
-  </si>
-  <si>
-    <t>C) Con una vía estrecha.</t>
-  </si>
-  <si>
     <t>imagenes/PT140820.png</t>
   </si>
   <si>
     <t>¿Qué efectos puede provocar un resfriado en la conducción?</t>
   </si>
   <si>
-    <t>A) Falta de coordinación y somnolencia</t>
-  </si>
-  <si>
-    <t>B) Desorientación</t>
-  </si>
-  <si>
-    <t>C) Somnolencia y pérdida de concentración</t>
-  </si>
-  <si>
     <t>imagenes/PT140821.png</t>
   </si>
   <si>
     <t>¿Qué sistemas ADAS están permitidos en las pruebas de control de aptitudes y comportamiento para la obtención del permiso de conducción?</t>
   </si>
   <si>
-    <t>A) El EBD o Aviso de frenada de emergencia y el LDW o Aviso de cambio involuntario de carril</t>
-  </si>
-  <si>
-    <t>B) El ISA o Control de velocidad adaptativo y el RCTA o Alerta de tráfico cruzado</t>
-  </si>
-  <si>
-    <t>C) El AEBS o Sistema de frenado de emergencia” y el Hill Holder o Sistema de salida en pendiente</t>
-  </si>
-  <si>
     <t>imagenes/PT140822.png</t>
   </si>
   <si>
     <t>Este conjunto de marcas blancas pintadas en la calzada...</t>
   </si>
   <si>
-    <t>A) obliga al vehículo a detenerse siempre.</t>
-  </si>
-  <si>
-    <t>B) indica que ningún conductor puede entrar con su vehículo o animal en esta zona.</t>
-  </si>
-  <si>
-    <t>C) indica un paso para peatones.</t>
-  </si>
-  <si>
     <t>imagenes/PT140823.png</t>
   </si>
   <si>
     <t>En esta vía, ¿a qué velocidad mínima está permitido circular con un turismo?</t>
   </si>
   <si>
-    <t>A) A 50 km/hora.</t>
-  </si>
-  <si>
-    <t>B) A 45 km/hora.</t>
-  </si>
-  <si>
-    <t>C) A 40 km/hora.</t>
-  </si>
-  <si>
     <t>imagenes/PT140824.png</t>
   </si>
   <si>
     <t>¿Puede adelantar por la derecha al vehículo rojo?</t>
   </si>
   <si>
-    <t>C) A veces, depende de la visibilidad.</t>
-  </si>
-  <si>
     <t>imagenes/PT140825.png</t>
   </si>
   <si>
     <t>La vía, su entorno y el propio vehículo, ¿pueden favorecer la aparición de distracciones al volante?</t>
   </si>
   <si>
-    <t>B) Sí, el vehículo y la vía pero no su entorno.</t>
-  </si>
-  <si>
-    <t>C) Sí, la vía pero no su entorno.</t>
-  </si>
-  <si>
     <t>imagenes/PT140826.png</t>
   </si>
   <si>
     <t>En el ámbito del tráfico, ¿a qué se llama grupos vulnerables?</t>
   </si>
   <si>
-    <t>A) A los jóvenes menores de 30 años que resultan heridos en un accidente.</t>
-  </si>
-  <si>
-    <t>B) A los grupos de población más propensos a sufrir un accidente.</t>
-  </si>
-  <si>
-    <t>C) A los pasajeros que resultan heridos en un accidente de automóvil.</t>
-  </si>
-  <si>
     <t>imagenes/PT140827.png</t>
   </si>
   <si>
     <t>En una vía interurbana insuficientemente iluminada, un vehículo circula a una velocidad inferior a 40 km/hora. ¿Podrá circular con el alumbrado de corto alcance?</t>
   </si>
   <si>
-    <t>A) No, tiene que utilizar el alumbrado de largo alcance de forma obligatoria.</t>
-  </si>
-  <si>
-    <t>C) Sí, pero también puede encender las luces largas si no deslumbra al resto de conductores.</t>
-  </si>
-  <si>
     <t>imagenes/PT140828.png</t>
   </si>
   <si>
     <t>¿Cuándo es la conducción más difícil y se es más propenso a sufrir un accidente?</t>
   </si>
   <si>
-    <t>A) Cuando circulan muchos vehículos ligeros</t>
-  </si>
-  <si>
-    <t>B) Cuando hay pocos vehículos en la vía</t>
-  </si>
-  <si>
-    <t>C) Cuando circulan muchos vehículos pesados</t>
-  </si>
-  <si>
     <t>imagenes/PT140829.png</t>
   </si>
   <si>
     <t>Cuando viaje con su mascota, ¿en qué lugar del vehículo podrá situarla para evitar que interfiera en la conducción?</t>
   </si>
   <si>
-    <t>A) Donde no comprometa su seguridad ni la del resto de pasajeros, además de ir sujeta con el dispositivo adecuado.</t>
-  </si>
-  <si>
-    <t>B) En los asientos traseros sujeta con el cinturón de seguridad como un pasajero más.</t>
-  </si>
-  <si>
-    <t>C) En el asiento delantero ya que si dispone de airbag frontal estará doblemente protegida.</t>
-  </si>
-  <si>
     <t>imagenes/PT140830.png</t>
+  </si>
+  <si>
+    <t>Sí, debe llevarlo abrochado hasta que el vehículo esté inmovilizado.</t>
+  </si>
+  <si>
+    <t>se desgastan más por los lados.</t>
+  </si>
+  <si>
+    <t>Sí.</t>
+  </si>
+  <si>
+    <t>Sí, puede haberse deteriorado el trenzado o los sistemas de anclaje.</t>
+  </si>
+  <si>
+    <t>que provoca una alteración del estado de ánimo que no es peligrosa para conducir.</t>
+  </si>
+  <si>
+    <t>Al final del carril de aceleración.</t>
+  </si>
+  <si>
+    <t>Sí, porque no es un vehículo a motor.</t>
+  </si>
+  <si>
+    <t>Sólo es necesario apagar el motor, las luces y la radio.</t>
+  </si>
+  <si>
+    <t>lo más aerodinámica posible, encorvando el cuerpo cuanto más mejor.</t>
+  </si>
+  <si>
+    <t>que tengan una MMA. no superior a 750 kg.</t>
+  </si>
+  <si>
+    <t>No, sólo pueden hacer señales ópticas</t>
+  </si>
+  <si>
+    <t>Una intersección con cuatro o más vías.</t>
+  </si>
+  <si>
+    <t>Las delanteras.</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>El titular del vehículo.</t>
+  </si>
+  <si>
+    <t>La señalización</t>
+  </si>
+  <si>
+    <t>A realizar un cambio de sentido.</t>
+  </si>
+  <si>
+    <t>Únicamente estará permitido en caso de urgencia</t>
+  </si>
+  <si>
+    <t>Sin preferencia de paso.</t>
+  </si>
+  <si>
+    <t>Falta de coordinación y somnolencia</t>
+  </si>
+  <si>
+    <t>El EBD o Aviso de frenada de emergencia y el LDW o Aviso de cambio involuntario de carril</t>
+  </si>
+  <si>
+    <t>obliga al vehículo a detenerse siempre.</t>
+  </si>
+  <si>
+    <t>A 50 km/hora.</t>
+  </si>
+  <si>
+    <t>A los jóvenes menores de 30 años que resultan heridos en un accidente.</t>
+  </si>
+  <si>
+    <t>No, tiene que utilizar el alumbrado de largo alcance de forma obligatoria.</t>
+  </si>
+  <si>
+    <t>Cuando circulan muchos vehículos ligeros</t>
+  </si>
+  <si>
+    <t>Donde no comprometa su seguridad ni la del resto de pasajeros, además de ir sujeta con el dispositivo adecuado.</t>
+  </si>
+  <si>
+    <t>No, no es obligatorio.</t>
+  </si>
+  <si>
+    <t>se desgastan más por el centro.</t>
+  </si>
+  <si>
+    <t>No, es aconsejable.</t>
+  </si>
+  <si>
+    <t>No, es un elemento de seguridad que no es necesario revisar nunca.</t>
+  </si>
+  <si>
+    <t>que siempre es leve.</t>
+  </si>
+  <si>
+    <t>Al principio del carril de aceleración.</t>
+  </si>
+  <si>
+    <t>No, porque son tranquilizantes.</t>
+  </si>
+  <si>
+    <t>Sólo es necesario apagar el motor y las luces.</t>
+  </si>
+  <si>
+    <t>un poco forzada, para evitar relajamientos.</t>
+  </si>
+  <si>
+    <t>que tengan una MMA. superior a 750 kg.</t>
+  </si>
+  <si>
+    <t>No, sólo pueden hacer señales acústicas</t>
+  </si>
+  <si>
+    <t>Una incorporación por la derecha.</t>
+  </si>
+  <si>
+    <t>Las traseras.</t>
+  </si>
+  <si>
+    <t>Nadie, por qué la inmovilización no tiene gastos.</t>
+  </si>
+  <si>
+    <t>Las condiciones de la vía</t>
+  </si>
+  <si>
+    <t>A detenerse.</t>
+  </si>
+  <si>
+    <t>Sí, está permitido y recomendado</t>
+  </si>
+  <si>
+    <t>Con preferencia de paso.</t>
+  </si>
+  <si>
+    <t>Desorientación</t>
+  </si>
+  <si>
+    <t>El ISA o Control de velocidad adaptativo y el RCTA o Alerta de tráfico cruzado</t>
+  </si>
+  <si>
+    <t>indica que ningún conductor puede entrar con su vehículo o animal en esta zona.</t>
+  </si>
+  <si>
+    <t>A 45 km/hora.</t>
+  </si>
+  <si>
+    <t>Sí, el vehículo y la vía pero no su entorno.</t>
+  </si>
+  <si>
+    <t>A los grupos de población más propensos a sufrir un accidente.</t>
+  </si>
+  <si>
+    <t>Cuando hay pocos vehículos en la vía</t>
+  </si>
+  <si>
+    <t>En los asientos traseros sujeta con el cinturón de seguridad como un pasajero más.</t>
+  </si>
+  <si>
+    <t>Solo podrá quitárselo si es taxista o repartidor.</t>
+  </si>
+  <si>
+    <t>se desgastan igual por los lados que por el centro.</t>
+  </si>
+  <si>
+    <t>Sólo si el cinturón no ha funcionado correctamente durante el accidente.</t>
+  </si>
+  <si>
+    <t>que puede ser peligrosa para conducir con seguridad.</t>
+  </si>
+  <si>
+    <t>Al principio o al final del carril de aceleración, es indiferente.</t>
+  </si>
+  <si>
+    <t>Sí, porque la vía es para peatones</t>
+  </si>
+  <si>
+    <t>No, porque retrasan la aparición de sueño.</t>
+  </si>
+  <si>
+    <t>Apagar el motor, las luces, los aparatos eléctricos y los teléfonos móviles.</t>
+  </si>
+  <si>
+    <t>suelta y no forzada, sin encorvar el cuerpo más de lo necesario.</t>
+  </si>
+  <si>
+    <t>cualquiera que sea su MMA.</t>
+  </si>
+  <si>
+    <t>Sí, pueden hacer señales ópticas y acústicas</t>
+  </si>
+  <si>
+    <t>Un paso a nivel con barreras.</t>
+  </si>
+  <si>
+    <t>Ningunas, la dirección está en la caja de cambios.</t>
+  </si>
+  <si>
+    <t>Sí, si la motocicleta supera los 125 cm3.</t>
+  </si>
+  <si>
+    <t>Los agentes de circulación.</t>
+  </si>
+  <si>
+    <t>El tipo de carburante</t>
+  </si>
+  <si>
+    <t>A extremar la precaución.</t>
+  </si>
+  <si>
+    <t>No, está prohibido</t>
+  </si>
+  <si>
+    <t>Con una vía estrecha.</t>
+  </si>
+  <si>
+    <t>Somnolencia y pérdida de concentración</t>
+  </si>
+  <si>
+    <t>El AEBS o Sistema de frenado de emergencia” y el Hill Holder o Sistema de salida en pendiente</t>
+  </si>
+  <si>
+    <t>indica un paso para peatones.</t>
+  </si>
+  <si>
+    <t>A 40 km/hora.</t>
+  </si>
+  <si>
+    <t>A veces, depende de la visibilidad.</t>
+  </si>
+  <si>
+    <t>Sí, la vía pero no su entorno.</t>
+  </si>
+  <si>
+    <t>A los pasajeros que resultan heridos en un accidente de automóvil.</t>
+  </si>
+  <si>
+    <t>Sí, pero también puede encender las luces largas si no deslumbra al resto de conductores.</t>
+  </si>
+  <si>
+    <t>Cuando circulan muchos vehículos pesados</t>
+  </si>
+  <si>
+    <t>En el asiento delantero ya que si dispone de airbag frontal estará doblemente protegida.</t>
   </si>
 </sst>
 </file>
@@ -912,599 +903,599 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="F2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="E9" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="E11" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>131</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" t="s">
         <v>32</v>
-      </c>
-      <c r="F13" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" t="s">
         <v>83</v>
       </c>
-      <c r="B17" t="s">
-        <v>84</v>
-      </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="E20" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>103</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>140</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>141</v>
       </c>
       <c r="E22" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
         <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F23" t="s">
-        <v>117</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="E24" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>128</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="E26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F29" t="s">
-        <v>143</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="C30" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>148</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>149</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" t="s">
+        <v>121</v>
+      </c>
+      <c r="D31" t="s">
         <v>150</v>
       </c>
-      <c r="C31" t="s">
-        <v>151</v>
-      </c>
-      <c r="D31" t="s">
-        <v>152</v>
-      </c>
       <c r="E31" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>68</v>
       </c>
     </row>
     <row r="196" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
